--- a/website_content_creation/authors/Emma-Isabella_Perry/Author_form.xlsx
+++ b/website_content_creation/authors/Emma-Isabella_Perry/Author_form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://041gc-my.sharepoint.com/personal/emily_smenderovac_nrcan-rncan_gc_ca/Documents/Documents/WET lab/GLFC-WET.github.io/website_content_creation/authors/Emma-Isabella_Perry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{399F1FEA-8655-4E6C-96E7-56F0F6422CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDF9E17E-4738-493A-A674-271DB4B4A844}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{399F1FEA-8655-4E6C-96E7-56F0F6422CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EFEE0F6-B1BE-4D49-B4C8-75173F24DB4A}"/>
   <bookViews>
-    <workbookView xWindow="1416" yWindow="1536" windowWidth="21624" windowHeight="11244" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14565" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -138,9 +138,6 @@
     <t>MSc student, Memorial University</t>
   </si>
   <si>
-    <t>Visiting and Co-supervised Students</t>
-  </si>
-  <si>
     <t>Environmental Science Biology Stream</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
   </si>
   <si>
     <t>https://mun.ca/grenfellcampus/</t>
+  </si>
+  <si>
+    <t>Past WETlab Members</t>
   </si>
 </sst>
 </file>
@@ -569,6 +569,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -578,10 +582,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -900,7 +900,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
@@ -920,7 +920,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -932,11 +932,11 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="38"/>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
@@ -951,7 +951,7 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="30" t="s">
         <v>32</v>
@@ -982,10 +982,10 @@
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="38"/>
+      <c r="B26" s="40"/>
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
@@ -996,11 +996,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="35" t="s">
         <v>40</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
